--- a/algorithm_source/pre_thk_cache/LC_M1_CU_CMP_M10.xlsx
+++ b/algorithm_source/pre_thk_cache/LC_M1_CU_CMP_M10.xlsx
@@ -475,14 +475,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6KTSD505_1</t>
+          <t>6KTSD503_2</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.877384580847714</v>
+        <v>0.3793709712037748</v>
       </c>
       <c r="D2" t="n">
-        <v>105</v>
+        <v>255</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -490,7 +490,7 @@
         </is>
       </c>
       <c r="F2" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -504,14 +504,14 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6KTSD506_2</t>
+          <t>6KTSD502_2</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>10.80656231640508</v>
+        <v>2.273711991572968</v>
       </c>
       <c r="D3" t="n">
-        <v>112</v>
+        <v>253</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -519,7 +519,7 @@
         </is>
       </c>
       <c r="F3" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -533,14 +533,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6KTSD508_2</t>
+          <t>6KTSD506_1</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-14.50429502481867</v>
+        <v>-2.047481363795806</v>
       </c>
       <c r="D4" t="n">
-        <v>113</v>
+        <v>217</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -548,7 +548,7 @@
         </is>
       </c>
       <c r="F4" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -562,14 +562,14 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6KTSD508_1</t>
+          <t>6KTSD505_1</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3.603074722604066</v>
+        <v>0.6876611875308367</v>
       </c>
       <c r="D5" t="n">
-        <v>125</v>
+        <v>227</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -577,7 +577,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -591,14 +591,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6KTSD501_1</t>
+          <t>6KTSD508_2</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>10.78002858713217</v>
+        <v>4.258769342144794</v>
       </c>
       <c r="D6" t="n">
-        <v>111</v>
+        <v>249</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -606,7 +606,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -620,14 +620,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6KTSD502_2</t>
+          <t>6KTSD502_1</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.273649032807205</v>
+        <v>-0.6338877489232358</v>
       </c>
       <c r="D7" t="n">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -635,7 +635,7 @@
         </is>
       </c>
       <c r="F7" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -649,14 +649,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6KTSD503_2</t>
+          <t>6KTSD503_1</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-9.637793117349664</v>
+        <v>-2.311504310241638</v>
       </c>
       <c r="D8" t="n">
-        <v>120</v>
+        <v>187</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -678,14 +678,14 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6KTSD505_2</t>
+          <t>6KTSD506_2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-5.510216712312306</v>
+        <v>8.285331727197251</v>
       </c>
       <c r="D9" t="n">
-        <v>133</v>
+        <v>221</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -693,7 +693,7 @@
         </is>
       </c>
       <c r="F9" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -707,14 +707,14 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>6KTSD501_2</t>
+          <t>6KTSD504_2</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-1.258186129558253</v>
+        <v>2.120269778959821</v>
       </c>
       <c r="D10" t="n">
-        <v>108</v>
+        <v>209</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="F10" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -736,14 +736,14 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6KTSD503_1</t>
+          <t>6KTSD504_1</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.5364221785217</v>
+        <v>2.446816321487665</v>
       </c>
       <c r="D11" t="n">
-        <v>100</v>
+        <v>229</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -765,14 +765,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6KTSD507_1</t>
+          <t>6KTSD507_2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.448199657188431</v>
+        <v>-2.866755451573184</v>
       </c>
       <c r="D12" t="n">
-        <v>102</v>
+        <v>193</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="F12" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -794,14 +794,14 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>6KTSD504_1</t>
+          <t>6KTSD501_1</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>10.17428134480539</v>
+        <v>1.523787272763975</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>225</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -809,7 +809,7 @@
         </is>
       </c>
       <c r="F13" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -823,14 +823,14 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>6KTSD502_1</t>
+          <t>6KTSD505_2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-3.172162576061612</v>
+        <v>1.510234644042808</v>
       </c>
       <c r="D14" t="n">
-        <v>180</v>
+        <v>245</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -838,7 +838,7 @@
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -852,14 +852,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6KTSD507_2</t>
+          <t>6KTSD501_2</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.729458937154178</v>
+        <v>1.076547807964781</v>
       </c>
       <c r="D15" t="n">
-        <v>162</v>
+        <v>207</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -867,7 +867,7 @@
         </is>
       </c>
       <c r="F15" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -881,14 +881,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>6KTSD504_2</t>
+          <t>6KTSD508_1</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-1.975678451767321</v>
+        <v>3.073655461608049</v>
       </c>
       <c r="D16" t="n">
-        <v>152</v>
+        <v>233</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -910,14 +910,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6KTSD506_1</t>
+          <t>6KTSD507_1</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.0549681750622315</v>
+        <v>4.476762205494595</v>
       </c>
       <c r="D17" t="n">
-        <v>174</v>
+        <v>203</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>46157.56617907283</v>
+        <v>46158.63406913155</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
